--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44589</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>46178</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>46162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45293</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45874</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45933</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>45940</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44656</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45267</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44744</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45933</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45145</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45471</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45145</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>45184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>44475</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45967</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45119</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45902</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45385</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45009</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45470</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45432</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44868</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46239</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45793</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45869</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45869</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44509</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44462</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44460</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44774</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44460</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>44586</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45266</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44744</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45371</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45173</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45173</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45317</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>44744</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44873</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45177</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>45154</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45481</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44956</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45293</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45316</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45562</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45043</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45243</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>46140</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45505</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>46140</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46140</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46140</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44934</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>46148</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45298</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45226</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45644</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>46163</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>46006</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45266</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45293</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45293</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>46027</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>46027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44865</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>46027</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45726</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46034</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>45617</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>46037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>46030</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>46176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45562</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46057</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45524</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>46041</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>46070</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46076</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>46077</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>46077</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>46077</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>46077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46077</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>46077</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>46185</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46086</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46086</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44485</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>46098</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46108</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44571</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44802</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45317</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44724</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44544</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>44802</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>46132</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46132</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45216</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45524</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44956</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44844</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44802</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45453</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>46273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45783</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45419</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45428</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>46239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45604</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44859</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45390</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44663</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45565</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45485</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44859</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE199"/>
+  <dimension ref="A1:AE197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4384-2022</t>
+          <t>A 25671-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44589</v>
+        <v>46178</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,26 +1920,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1951,18 +1951,139 @@
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
       </c>
       <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav
+Fjällig taggsvamp s.str.
+Vedskivlav
+Vedtrappmossa
+Blåsippa
+Spillkråka
+Tjäder
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 25671-2026 artfynd.xlsx", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 25671-2026 karta.png", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 25671-2026 georefererad karta.tif", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 25671-2026 FSC-klagomål.docx", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 25671-2026 FSC-klagomål mail.docx", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 25671-2026 tillsynsbegäran.docx", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 25671-2026 tillsynsbegäran mail.docx", "A 25671-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 25671-2026 prioriterade fågelarter.docx", "A 25671-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 4384-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44589</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
         <v>19</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Knärot
@@ -1974,157 +2095,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 4384-2022 artfynd.xlsx", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 4384-2022 karta.png", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 4384-2022 georefererad karta.tif", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/knärot/A 4384-2022 karta knärot.png", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 4384-2022 FSC-klagomål.docx", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 4384-2022 FSC-klagomål mail.docx", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 4384-2022 tillsynsbegäran.docx", "A 4384-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 4384-2022 tillsynsbegäran mail.docx", "A 4384-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25671-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>12</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav
-Fjällig taggsvamp s.str.
-Vedskivlav
-Vedtrappmossa
-Blåsippa
-Spillkråka
-Tjäder
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 25671-2026 artfynd.xlsx", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 25671-2026 karta.png", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 25671-2026 georefererad karta.tif", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 25671-2026 FSC-klagomål.docx", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 25671-2026 FSC-klagomål mail.docx", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 25671-2026 tillsynsbegäran.docx", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 25671-2026 tillsynsbegäran mail.docx", "A 25671-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 25671-2026 prioriterade fågelarter.docx", "A 25671-2026")</f>
         <v/>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57411-2025</t>
+          <t>A 36854-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45980</v>
+        <v>45874</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,14 +2381,19 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -2415,12 +2420,245 @@
         <v>6</v>
       </c>
       <c r="T16" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp
+Rödgul trumpetsvamp
+Mattlummer
+Spillkråka
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 36854-2025 artfynd.xlsx", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 36854-2025 karta.png", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 36854-2025 georefererad karta.tif", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 36854-2025 FSC-klagomål.docx", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 36854-2025 FSC-klagomål mail.docx", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 36854-2025 tillsynsbegäran.docx", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 36854-2025 tillsynsbegäran mail.docx", "A 36854-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 36854-2025 prioriterade fågelarter.docx", "A 36854-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 23357-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Dvärgslinke
+Spädslinke
+Bred kärrtrollslända
+Citronfläckad kärrtrollslända
+Pudrad kärrtrollslända
+Trana</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 23357-2026 artfynd.xlsx", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 23357-2026 karta.png", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 23357-2026 georefererad karta.tif", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 23357-2026 FSC-klagomål.docx", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 23357-2026 FSC-klagomål mail.docx", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 23357-2026 tillsynsbegäran.docx", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 23357-2026 tillsynsbegäran mail.docx", "A 23357-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 23357-2026 prioriterade fågelarter.docx", "A 23357-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57411-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>8</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Grön sköldmossa
@@ -2430,226 +2668,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 57411-2025 artfynd.xlsx", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 57411-2025 karta.png", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 57411-2025 georefererad karta.tif", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 57411-2025 FSC-klagomål.docx", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 57411-2025 FSC-klagomål mail.docx", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 57411-2025 tillsynsbegäran.docx", "A 57411-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 57411-2025 tillsynsbegäran mail.docx", "A 57411-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 23357-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 97-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="D19" s="1" t="n">
+        <v>45293</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Dvärgslinke
-Spädslinke
-Bred kärrtrollslända
-Citronfläckad kärrtrollslända
-Pudrad kärrtrollslända
-Trana</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 23357-2026 artfynd.xlsx", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 23357-2026 karta.png", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 23357-2026 georefererad karta.tif", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 23357-2026 FSC-klagomål.docx", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 23357-2026 FSC-klagomål mail.docx", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 23357-2026 tillsynsbegäran.docx", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 23357-2026 tillsynsbegäran mail.docx", "A 23357-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 23357-2026 prioriterade fågelarter.docx", "A 23357-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 97-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45293</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Nordfladdermus
@@ -2659,151 +2778,32 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 97-2024 artfynd.xlsx", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 97-2024 karta.png", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 97-2024 georefererad karta.tif", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 97-2024 FSC-klagomål.docx", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 97-2024 FSC-klagomål mail.docx", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 97-2024 tillsynsbegäran.docx", "A 97-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 97-2024 tillsynsbegäran mail.docx", "A 97-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 36854-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45874</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>11</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp
-Rödgul trumpetsvamp
-Mattlummer
-Spillkråka
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 36854-2025 artfynd.xlsx", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 36854-2025 karta.png", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 36854-2025 georefererad karta.tif", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 36854-2025 FSC-klagomål.docx", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 36854-2025 FSC-klagomål mail.docx", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 36854-2025 tillsynsbegäran.docx", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 36854-2025 tillsynsbegäran mail.docx", "A 36854-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 36854-2025 prioriterade fågelarter.docx", "A 36854-2025")</f>
         <v/>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45933</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45610</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>45940</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44656</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62320-2023</t>
+          <t>A 9205-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45267</v>
+        <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3664,9 +3664,121 @@
         <v>4</v>
       </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Björksplintborre
+Gullgröppa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 9205-2026 artfynd.xlsx", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 9205-2026 karta.png", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 9205-2026 georefererad karta.tif", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 9205-2026 FSC-klagomål.docx", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 9205-2026 FSC-klagomål mail.docx", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 9205-2026 tillsynsbegäran.docx", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 9205-2026 tillsynsbegäran mail.docx", "A 9205-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 9205-2026 prioriterade fågelarter.docx", "A 9205-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 62320-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>4</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Vedskivlav
@@ -3674,144 +3786,32 @@
 Jättesvampmal</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 62320-2023 artfynd.xlsx", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 62320-2023 karta.png", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 62320-2023 georefererad karta.tif", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 62320-2023 FSC-klagomål.docx", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 62320-2023 FSC-klagomål mail.docx", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 62320-2023 tillsynsbegäran.docx", "A 62320-2023")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 62320-2023 tillsynsbegäran mail.docx", "A 62320-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 9205-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Björksplintborre
-Gullgröppa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 9205-2026 artfynd.xlsx", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 9205-2026 karta.png", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 9205-2026 georefererad karta.tif", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 9205-2026 FSC-klagomål.docx", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 9205-2026 FSC-klagomål mail.docx", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 9205-2026 tillsynsbegäran.docx", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 9205-2026 tillsynsbegäran mail.docx", "A 9205-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 9205-2026 prioriterade fågelarter.docx", "A 9205-2026")</f>
         <v/>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         <v>44744</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45933</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45145</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45471</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45145</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43525-2023</t>
+          <t>A 55044-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45184</v>
+        <v>45967</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4830,22 +4830,17 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4860,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4869,266 +4864,271 @@
         <v>2</v>
       </c>
       <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 55044-2025 artfynd.xlsx", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 55044-2025 karta.png", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 55044-2025 georefererad karta.tif", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 55044-2025 FSC-klagomål.docx", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 55044-2025 FSC-klagomål mail.docx", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 55044-2025 tillsynsbegäran.docx", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 55044-2025 tillsynsbegäran mail.docx", "A 55044-2025")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 55044-2025 prioriterade fågelarter.docx", "A 55044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A 43525-2023</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="n">
         <v>6</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>6</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Slåtterfibbla
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 43525-2023 artfynd.xlsx", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 43525-2023 karta.png", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 43525-2023 georefererad karta.tif", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 43525-2023 FSC-klagomål.docx", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 43525-2023 FSC-klagomål mail.docx", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 43525-2023 tillsynsbegäran.docx", "A 43525-2023")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 43525-2023 tillsynsbegäran mail.docx", "A 43525-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>A 55263-2021</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>44475</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
+      <c r="E40" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>2.3</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>2</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T40" t="n">
         <v>2</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Reliktbock</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 55263-2021 artfynd.xlsx", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 55263-2021 karta.png", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 55263-2021 georefererad karta.tif", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 55263-2021 FSC-klagomål.docx", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 55263-2021 FSC-klagomål mail.docx", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 55263-2021 tillsynsbegäran.docx", "A 55263-2021")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 55263-2021 tillsynsbegäran mail.docx", "A 55263-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 55044-2025</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>45967</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 55044-2025 artfynd.xlsx", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 55044-2025 karta.png", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 55044-2025 georefererad karta.tif", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 55044-2025 FSC-klagomål.docx", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 55044-2025 FSC-klagomål mail.docx", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 55044-2025 tillsynsbegäran.docx", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 55044-2025 tillsynsbegäran mail.docx", "A 55044-2025")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 55044-2025 prioriterade fågelarter.docx", "A 55044-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10263-2025</t>
+          <t>A 3711-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45720</v>
+        <v>46043</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5158,16 +5158,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5191,374 +5191,374 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 3711-2026 artfynd.xlsx", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 3711-2026 karta.png", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="Y41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 3711-2026 georefererad karta.tif", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 3711-2026 FSC-klagomål.docx", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 3711-2026 FSC-klagomål mail.docx", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 3711-2026 tillsynsbegäran.docx", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 3711-2026 tillsynsbegäran mail.docx", "A 3711-2026")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 3711-2026 prioriterade fågelarter.docx", "A 3711-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A 10263-2025</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45720</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 10263-2025 artfynd.xlsx", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 10263-2025 karta.png", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 10263-2025 georefererad karta.tif", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 10263-2025 FSC-klagomål.docx", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 10263-2025 FSC-klagomål mail.docx", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 10263-2025 tillsynsbegäran.docx", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 10263-2025 tillsynsbegäran mail.docx", "A 10263-2025")</f>
         <v/>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 10263-2025 prioriterade fågelarter.docx", "A 10263-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>A 16478-2025</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D43" s="1" t="n">
         <v>45751</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+      <c r="E43" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
         <v>2.1</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>2</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>2</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T43" t="n">
         <v>3</v>
       </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>Myskbock
 Tibast</t>
         </is>
       </c>
-      <c r="W42">
+      <c r="W43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 16478-2025 artfynd.xlsx", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="X42">
+      <c r="X43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 16478-2025 karta.png", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 16478-2025 georefererad karta.tif", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="AA42">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 16478-2025 FSC-klagomål.docx", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="AB42">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 16478-2025 FSC-klagomål mail.docx", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="AC42">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 16478-2025 tillsynsbegäran.docx", "A 16478-2025")</f>
         <v/>
       </c>
-      <c r="AD42">
+      <c r="AD43">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 16478-2025 tillsynsbegäran mail.docx", "A 16478-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>A 16724-2022</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D44" s="1" t="n">
         <v>44673</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="E44" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SÖDERTÄLJE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I44" t="n">
         <v>2.7</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
         <v>2</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S44" t="n">
         <v>2</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T44" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U44" t="n">
         <v>1</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Stor bockrot
 Gullpudra</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 16724-2022 artfynd.xlsx", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 16724-2022 karta.png", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 16724-2022 georefererad karta.tif", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 16724-2022 FSC-klagomål.docx", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 16724-2022 FSC-klagomål mail.docx", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 16724-2022 tillsynsbegäran.docx", "A 16724-2022")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 16724-2022 tillsynsbegäran mail.docx", "A 16724-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 3711-2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>46043</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 3711-2026 artfynd.xlsx", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 3711-2026 karta.png", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 3711-2026 georefererad karta.tif", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 3711-2026 FSC-klagomål.docx", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 3711-2026 FSC-klagomål mail.docx", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 3711-2026 tillsynsbegäran.docx", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 3711-2026 tillsynsbegäran mail.docx", "A 3711-2026")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 3711-2026 prioriterade fågelarter.docx", "A 3711-2026")</f>
         <v/>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45119</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45902</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45385</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45009</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45470</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19793-2024</t>
+          <t>A 30565-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45432</v>
+        <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,11 +7012,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7056,42 +7056,42 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 19793-2024 artfynd.xlsx", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 30565-2026 artfynd.xlsx", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 19793-2024 karta.png", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 30565-2026 karta.png", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 19793-2024 georefererad karta.tif", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 30565-2026 georefererad karta.tif", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 19793-2024 FSC-klagomål.docx", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 30565-2026 FSC-klagomål.docx", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 19793-2024 FSC-klagomål mail.docx", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 30565-2026 FSC-klagomål mail.docx", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 19793-2024 tillsynsbegäran.docx", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 30565-2026 tillsynsbegäran.docx", "A 30565-2026")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 19793-2024 tillsynsbegäran mail.docx", "A 19793-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 30565-2026 tillsynsbegäran mail.docx", "A 30565-2026")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56596-2023</t>
+          <t>A 19793-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45243</v>
+        <v>45432</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7120,18 +7120,23 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>1</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
@@ -7145,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -7161,42 +7166,42 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 56596-2023 artfynd.xlsx", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 19793-2024 artfynd.xlsx", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 56596-2023 karta.png", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 19793-2024 karta.png", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 56596-2023 georefererad karta.tif", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 19793-2024 georefererad karta.tif", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 56596-2023 FSC-klagomål.docx", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 19793-2024 FSC-klagomål.docx", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 56596-2023 FSC-klagomål mail.docx", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 19793-2024 FSC-klagomål mail.docx", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 56596-2023 tillsynsbegäran.docx", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 19793-2024 tillsynsbegäran.docx", "A 19793-2024")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 56596-2023 tillsynsbegäran mail.docx", "A 56596-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 19793-2024 tillsynsbegäran mail.docx", "A 19793-2024")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30565-2026</t>
+          <t>A 56596-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7210,10 +7215,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>45243</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,22 +7230,17 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -7271,42 +7271,42 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 30565-2026 artfynd.xlsx", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 56596-2023 artfynd.xlsx", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 30565-2026 karta.png", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 56596-2023 karta.png", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 30565-2026 georefererad karta.tif", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 56596-2023 georefererad karta.tif", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 30565-2026 FSC-klagomål.docx", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 56596-2023 FSC-klagomål.docx", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 30565-2026 FSC-klagomål mail.docx", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 56596-2023 FSC-klagomål mail.docx", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 30565-2026 tillsynsbegäran.docx", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 56596-2023 tillsynsbegäran.docx", "A 56596-2023")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 30565-2026 tillsynsbegäran mail.docx", "A 30565-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 56596-2023 tillsynsbegäran mail.docx", "A 56596-2023")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52046-2022</t>
+          <t>A 32522-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44868</v>
+        <v>46239</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,13 +7335,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7381,42 +7376,42 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 52046-2022 artfynd.xlsx", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 32522-2026 artfynd.xlsx", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 52046-2022 karta.png", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 32522-2026 karta.png", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 52046-2022 georefererad karta.tif", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 32522-2026 georefererad karta.tif", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 52046-2022 FSC-klagomål.docx", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 32522-2026 FSC-klagomål.docx", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 52046-2022 FSC-klagomål mail.docx", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 32522-2026 FSC-klagomål mail.docx", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 52046-2022 tillsynsbegäran.docx", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 32522-2026 tillsynsbegäran.docx", "A 32522-2026")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 52046-2022 tillsynsbegäran mail.docx", "A 52046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 32522-2026 tillsynsbegäran mail.docx", "A 32522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33892-2022</t>
+          <t>A 52046-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7430,10 +7425,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44790</v>
+        <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,18 +7440,23 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -7482,50 +7482,46 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 33892-2022 artfynd.xlsx", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 52046-2022 artfynd.xlsx", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 33892-2022 karta.png", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 52046-2022 karta.png", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 33892-2022 georefererad karta.tif", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 52046-2022 georefererad karta.tif", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 33892-2022 FSC-klagomål.docx", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 52046-2022 FSC-klagomål.docx", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 33892-2022 FSC-klagomål mail.docx", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 52046-2022 FSC-klagomål mail.docx", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 33892-2022 tillsynsbegäran.docx", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 52046-2022 tillsynsbegäran.docx", "A 52046-2022")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 33892-2022 tillsynsbegäran mail.docx", "A 33892-2022")</f>
-        <v/>
-      </c>
-      <c r="AE62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 33892-2022 prioriterade fågelarter.docx", "A 33892-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 52046-2022 tillsynsbegäran mail.docx", "A 52046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32522-2026</t>
+          <t>A 33892-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7539,10 +7535,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46239</v>
+        <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,16 +7551,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7579,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -7591,39 +7587,43 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 32522-2026 artfynd.xlsx", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/artfynd/A 33892-2022 artfynd.xlsx", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 32522-2026 karta.png", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor/A 33892-2022 karta.png", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 32522-2026 georefererad karta.tif", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/kartor_geotiff/A 33892-2022 georefererad karta.tif", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 32522-2026 FSC-klagomål.docx", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomål/A 33892-2022 FSC-klagomål.docx", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 32522-2026 FSC-klagomål mail.docx", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/klagomålsmail/A 33892-2022 FSC-klagomål mail.docx", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 32522-2026 tillsynsbegäran.docx", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsyn/A 33892-2022 tillsynsbegäran.docx", "A 33892-2022")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 32522-2026 tillsynsbegäran mail.docx", "A 32522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/tillsynsmail/A 33892-2022 tillsynsbegäran mail.docx", "A 33892-2022")</f>
+        <v/>
+      </c>
+      <c r="AE63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0181/fåglar/A 33892-2022 prioriterade fågelarter.docx", "A 33892-2022")</f>
         <v/>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
         <v>45793</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45869</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45869</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44509</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44462</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51454-2021</t>
+          <t>A 16437-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44460</v>
+        <v>44671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16437-2022</t>
+          <t>A 31429-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44671</v>
+        <v>44774</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8583,7 +8583,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31429-2022</t>
+          <t>A 3585-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44774</v>
+        <v>44586</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8656,7 +8656,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51482-2021</t>
+          <t>A 62311-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44460</v>
+        <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8729,7 +8729,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3585-2022</t>
+          <t>A 27970-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44586</v>
+        <v>44744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8802,7 +8802,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62311-2023</t>
+          <t>A 3382-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8812,14 +8812,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45266</v>
+        <v>45317</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27970-2022</t>
+          <t>A 27969-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8892,7 +8892,7 @@
         <v>44744</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8948,7 +8948,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56349-2023</t>
+          <t>A 11319-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45243</v>
+        <v>45371</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -9021,7 +9021,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11319-2024</t>
+          <t>A 56349-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45371</v>
+        <v>45243</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -9094,7 +9094,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41111-2023</t>
+          <t>A 28981-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45173</v>
+        <v>45104</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -9167,7 +9167,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41115-2023</t>
+          <t>A 41111-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9184,7 +9184,7 @@
         <v>45173</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3382-2024</t>
+          <t>A 41115-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9250,14 +9250,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45317</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9313,7 +9313,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27969-2022</t>
+          <t>A 52101-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9323,14 +9323,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44744</v>
+        <v>44873</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9342,8 +9342,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9386,7 +9391,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28981-2023</t>
+          <t>A 37844-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9396,14 +9401,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45104</v>
+        <v>44810</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9416,7 +9421,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>12.2</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9459,7 +9464,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37844-2022</t>
+          <t>A 42133-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9469,14 +9474,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44810</v>
+        <v>45177</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9489,7 +9494,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9532,7 +9537,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52101-2022</t>
+          <t>A 36886-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9546,10 +9551,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44873</v>
+        <v>45154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,13 +9566,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9610,7 +9610,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42133-2023</t>
+          <t>A 4443-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45177</v>
+        <v>44956</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9683,7 +9683,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36886-2023</t>
+          <t>A 28982-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9697,10 +9697,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45154</v>
+        <v>45481</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9756,7 +9756,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28982-2024</t>
+          <t>A 25412-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9766,14 +9766,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45481</v>
+        <v>45799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>6.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4443-2023</t>
+          <t>A 92-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44956</v>
+        <v>45293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9902,7 +9902,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 92-2024</t>
+          <t>A 25415-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45293</v>
+        <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9975,7 +9975,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25412-2025</t>
+          <t>A 20603-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45799</v>
+        <v>46140</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45316</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45562</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18592-2023</t>
+          <t>A 48046-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45043</v>
+        <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10525,8 +10525,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10569,7 +10574,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1381-2023</t>
+          <t>A 20582-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10583,10 +10588,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44936</v>
+        <v>46140</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10599,7 +10604,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10642,7 +10647,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56354-2023</t>
+          <t>A 20596-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10656,10 +10661,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45243</v>
+        <v>46140</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10672,7 +10677,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10715,7 +10720,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25415-2025</t>
+          <t>A 18592-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10729,10 +10734,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45799</v>
+        <v>45043</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10745,7 +10750,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>10.8</v>
+        <v>4.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10788,7 +10793,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20603-2026</t>
+          <t>A 20579-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10805,7 +10810,7 @@
         <v>46140</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10818,7 +10823,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10861,7 +10866,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31375-2024</t>
+          <t>A 20591-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10871,14 +10876,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45505</v>
+        <v>46140</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10890,13 +10895,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20582-2026</t>
+          <t>A 1381-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10953,10 +10953,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46140</v>
+        <v>44936</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20596-2026</t>
+          <t>A 56354-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46140</v>
+        <v>45243</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -11085,7 +11085,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20579-2026</t>
+          <t>A 21483-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11095,14 +11095,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -11158,7 +11158,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20591-2026</t>
+          <t>A 31375-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11168,14 +11168,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46140</v>
+        <v>45505</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11187,8 +11187,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11248,7 +11253,7 @@
         <v>44934</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11321,7 +11326,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11377,7 +11382,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48046-2025</t>
+          <t>A 10446-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11391,10 +11396,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45932</v>
+        <v>46077</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11406,13 +11411,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21483-2026</t>
+          <t>A 23632-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11465,14 +11465,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46148</v>
+        <v>46163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11484,8 +11484,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11545,7 +11550,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11618,7 +11623,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11691,7 +11696,7 @@
         <v>45298</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11747,7 +11752,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47576-2023</t>
+          <t>A 1150-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11761,10 +11766,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45197</v>
+        <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11777,7 +11782,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11820,7 +11825,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35906-2022</t>
+          <t>A 25288-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11830,14 +11835,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44802</v>
+        <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11849,8 +11854,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11893,7 +11903,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 52815-2023</t>
+          <t>A 62047-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11907,10 +11917,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45226</v>
+        <v>46006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11922,13 +11932,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11971,7 +11976,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60635-2024</t>
+          <t>A 62049-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45644</v>
+        <v>46006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12001,7 +12006,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>10.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -12044,7 +12049,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 10446-2026</t>
+          <t>A 47576-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12058,10 +12063,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46077</v>
+        <v>45197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12074,7 +12079,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -12117,7 +12122,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23632-2026</t>
+          <t>A 35906-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12127,14 +12132,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46163</v>
+        <v>44802</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12146,13 +12151,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12195,7 +12195,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62047-2025</t>
+          <t>A 52815-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12209,10 +12209,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46006</v>
+        <v>45226</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12224,8 +12224,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12268,7 +12273,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 62049-2025</t>
+          <t>A 234-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12282,10 +12287,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12298,7 +12303,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12341,7 +12346,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 62311-2023</t>
+          <t>A 243-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12355,10 +12360,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45266</v>
+        <v>46027</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12371,7 +12376,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12414,7 +12419,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 25706-2023</t>
+          <t>A 231-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12428,10 +12433,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45090</v>
+        <v>46027</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12444,7 +12449,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12487,7 +12492,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22-2024</t>
+          <t>A 233-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12501,10 +12506,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45293</v>
+        <v>46027</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12517,7 +12522,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12560,7 +12565,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 95-2024</t>
+          <t>A 1696-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12574,10 +12579,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45293</v>
+        <v>46034</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12590,7 +12595,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12633,7 +12638,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 234-2026</t>
+          <t>A 1715-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12647,10 +12652,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46027</v>
+        <v>46034</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12663,7 +12668,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12706,7 +12711,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 243-2026</t>
+          <t>A 27006-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12716,14 +12721,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46027</v>
+        <v>46185</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12736,7 +12741,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12779,7 +12784,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49956-2022</t>
+          <t>A 27257-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12793,10 +12798,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44865</v>
+        <v>46188</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12809,7 +12814,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12852,7 +12857,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 231-2026</t>
+          <t>A 2685-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12866,10 +12871,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12882,7 +12887,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12925,7 +12930,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 233-2026</t>
+          <t>A 60635-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12939,10 +12944,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46027</v>
+        <v>45644</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12955,7 +12960,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12998,7 +13003,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 1696-2026</t>
+          <t>A 7023-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -13012,10 +13017,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13028,7 +13033,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -13071,7 +13076,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11343-2025</t>
+          <t>A 28175-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -13081,14 +13086,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45726</v>
+        <v>46195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13101,7 +13106,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13144,7 +13149,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1715-2026</t>
+          <t>A 3152-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13154,14 +13159,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13174,7 +13179,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13217,7 +13222,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54596-2024</t>
+          <t>A 9234-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13231,10 +13236,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45617</v>
+        <v>46070</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13247,7 +13252,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13290,7 +13295,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2685-2026</t>
+          <t>A 62311-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13304,10 +13309,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46037</v>
+        <v>45266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13320,7 +13325,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13363,7 +13368,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 45145-2022</t>
+          <t>A 25706-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13377,10 +13382,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44844</v>
+        <v>45090</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13393,7 +13398,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13436,7 +13441,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1150-2026</t>
+          <t>A 10327-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13450,10 +13455,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46030</v>
+        <v>46076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13465,8 +13470,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13509,7 +13519,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25288-2026</t>
+          <t>A 10414-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13523,10 +13533,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46176</v>
+        <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13538,13 +13548,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13587,7 +13592,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 42339-2024</t>
+          <t>A 10426-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13597,14 +13602,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45562</v>
+        <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13616,13 +13621,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13665,7 +13665,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7023-2026</t>
+          <t>A 10425-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13679,10 +13679,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46057</v>
+        <v>46077</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 48820-2022</t>
+          <t>A 10450-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13752,10 +13752,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44859</v>
+        <v>46077</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13767,13 +13767,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13816,7 +13811,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 34193-2024</t>
+          <t>A 10452-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13830,10 +13825,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45524</v>
+        <v>46077</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13846,7 +13841,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13889,7 +13884,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3152-2026</t>
+          <t>A 10404-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13899,14 +13894,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46041</v>
+        <v>46077</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13919,7 +13914,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13962,7 +13957,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 9234-2026</t>
+          <t>A 22-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13976,10 +13971,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46070</v>
+        <v>45293</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13992,7 +13987,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -14035,7 +14030,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26812-2022</t>
+          <t>A 95-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -14049,10 +14044,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44740</v>
+        <v>45293</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14065,7 +14060,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -14108,7 +14103,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10327-2026</t>
+          <t>A 12116-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -14122,10 +14117,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14137,13 +14132,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -14186,7 +14176,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10414-2026</t>
+          <t>A 12121-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14200,10 +14190,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14216,7 +14206,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14259,7 +14249,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10426-2026</t>
+          <t>A 49956-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14273,10 +14263,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46077</v>
+        <v>44865</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14289,7 +14279,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14332,7 +14322,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10425-2026</t>
+          <t>A 11343-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14346,10 +14336,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46077</v>
+        <v>45726</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14405,7 +14395,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 10450-2026</t>
+          <t>A 54596-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14419,10 +14409,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46077</v>
+        <v>45617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14435,7 +14425,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.3</v>
+        <v>9.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14478,7 +14468,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10452-2026</t>
+          <t>A 13943-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14492,10 +14482,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46077</v>
+        <v>46098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14508,7 +14498,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14551,7 +14541,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10404-2026</t>
+          <t>A 45145-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14565,10 +14555,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46077</v>
+        <v>44844</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14581,7 +14571,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14624,7 +14614,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27006-2026</t>
+          <t>A 15964-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14634,14 +14624,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46185</v>
+        <v>46108</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14654,7 +14644,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14697,7 +14687,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27257-2026</t>
+          <t>A 42339-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14707,14 +14697,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46188</v>
+        <v>45562</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14726,8 +14716,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14770,7 +14765,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12116-2026</t>
+          <t>A 48820-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14784,10 +14779,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46086</v>
+        <v>44859</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14799,8 +14794,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14843,7 +14843,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12121-2026</t>
+          <t>A 34193-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14857,10 +14857,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46086</v>
+        <v>45524</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14916,7 +14916,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 57884-2021</t>
+          <t>A 19071-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14930,10 +14930,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44485</v>
+        <v>46132</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14989,7 +14989,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6886-2022</t>
+          <t>A 19078-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -15003,10 +15003,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44602</v>
+        <v>46132</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -15062,7 +15062,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13943-2026</t>
+          <t>A 26812-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -15076,10 +15076,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46098</v>
+        <v>44740</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -15135,7 +15135,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28175-2026</t>
+          <t>A 57884-2021</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15145,14 +15145,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46195</v>
+        <v>44485</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 15964-2026</t>
+          <t>A 6886-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15222,10 +15222,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46108</v>
+        <v>44602</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15298,7 +15298,7 @@
         <v>44571</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44802</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45317</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44724</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44544</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>44802</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 19071-2026</t>
+          <t>A 36938-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15884,10 +15884,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46132</v>
+        <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15943,7 +15943,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 19078-2026</t>
+          <t>A 51931-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46132</v>
+        <v>45216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -16016,7 +16016,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 51931-2023</t>
+          <t>A 34194-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16030,10 +16030,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45216</v>
+        <v>45524</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -16089,7 +16089,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34194-2024</t>
+          <t>A 4440-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16103,10 +16103,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45524</v>
+        <v>44956</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.1</v>
+        <v>18.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 4440-2023</t>
+          <t>A 1759-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16176,10 +16176,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44956</v>
+        <v>45671</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>18.4</v>
+        <v>3.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16235,7 +16235,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 1759-2025</t>
+          <t>A 45184-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16249,10 +16249,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45671</v>
+        <v>44844</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16308,7 +16308,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45184-2022</t>
+          <t>A 32518-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16322,10 +16322,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44844</v>
+        <v>46239</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16398,7 +16398,7 @@
         <v>44943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44802</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45453</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36938-2026</t>
+          <t>A 21726-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46273</v>
+        <v>45783</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16819,7 +16819,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 21726-2025</t>
+          <t>A 47977-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16833,10 +16833,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45783</v>
+        <v>44855</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16892,7 +16892,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 47977-2022</t>
+          <t>A 17979-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16906,10 +16906,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44855</v>
+        <v>45419</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16965,7 +16965,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17979-2024</t>
+          <t>A 19210-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16975,14 +16975,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -17038,7 +17038,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19210-2024</t>
+          <t>A 51353-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17048,14 +17048,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45428</v>
+        <v>45604</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -17111,24 +17111,24 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32518-2026</t>
+          <t>S 6029-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46239</v>
+        <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17140,8 +17140,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17184,24 +17189,24 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 51353-2024</t>
+          <t>S 1081-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45604</v>
+        <v>45390</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17214,7 +17219,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17257,7 +17262,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 6029-2022</t>
+          <t>S 1920-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17267,14 +17272,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44859</v>
+        <v>44663</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17288,11 +17293,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17335,7 +17340,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 1081-2024</t>
+          <t>S 3931-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17349,10 +17354,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45390</v>
+        <v>45565</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17365,7 +17370,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17408,7 +17413,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 1920-2022</t>
+          <t>S 2770-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17418,14 +17423,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44663</v>
+        <v>45485</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17437,13 +17442,8 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17486,7 +17486,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 3931-2024</t>
+          <t>S 4009-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45565</v>
+        <v>45571</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17556,10 +17556,10 @@
       </c>
       <c r="V196" s="2" t="inlineStr"/>
     </row>
-    <row r="197" ht="15" customHeight="1">
+    <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 2770-2024</t>
+          <t>S 6039-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17573,10 +17573,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45485</v>
+        <v>44859</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17588,8 +17588,13 @@
           <t>SÖDERTÄLJE</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17628,157 +17633,6 @@
         <v>0</v>
       </c>
       <c r="V197" s="2" t="inlineStr"/>
-    </row>
-    <row r="198" ht="15" customHeight="1">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>S 4009-2024</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>45571</v>
-      </c>
-      <c r="E198" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0</v>
-      </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="n">
-        <v>0</v>
-      </c>
-      <c r="V198" s="2" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>S 6039-2022</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>44859</v>
-      </c>
-      <c r="E199" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>SÖDERTÄLJE</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I199" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>0</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" t="n">
-        <v>0</v>
-      </c>
-      <c r="U199" t="n">
-        <v>0</v>
-      </c>
-      <c r="V199" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44840</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>46178</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45293</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>46162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45148</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45933</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>44744</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45267</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45940</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44656</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45933</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>44520</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45471</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45145</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44475</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45967</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45385</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45119</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44868</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>45869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45009</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45432</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45243</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>46239</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44509</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44586</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44671</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44774</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45266</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45226</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45317</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45604</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44865</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>46034</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>46037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44977</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45644</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>46057</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44544</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44564</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46070</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>46041</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46077</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>46077</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>46077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>46077</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>46077</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>46076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45541</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45562</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>46086</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>46086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44943</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44744</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46098</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44956</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44744</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>46108</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45316</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44844</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44571</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>46132</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46132</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45243</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44936</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45524</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>46140</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>46140</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45298</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44485</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46077</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>46163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45726</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44724</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45173</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45173</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>46185</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46188</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44586</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45385</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45240</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45250</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44740</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45266</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45317</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44802</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45293</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45435</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>46273</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44802</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45562</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44802</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45371</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45617</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44873</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45090</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45216</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44934</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45293</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45783</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45419</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45428</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44663</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45390</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45565</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45485</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45571</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44859</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44840</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>46178</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45293</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>46162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45148</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45933</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>44744</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45267</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45940</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44656</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45933</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>44520</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44868</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45471</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45145</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44475</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45967</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45385</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45119</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44868</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>45869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45009</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45432</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45243</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>46239</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44509</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44586</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44671</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44774</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45266</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>45243</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45226</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45317</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45604</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44865</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>46034</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>46037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44977</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45644</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>46057</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44544</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44564</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46070</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>46041</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46077</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>46077</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>46077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>46077</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>46077</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>46076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45541</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45562</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>46086</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>46086</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44943</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44744</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46098</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44956</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44744</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>46108</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45316</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44844</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44571</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>46132</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46132</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>46140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45243</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44936</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45524</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>46140</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>46140</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45298</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44485</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46077</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>46163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45726</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44724</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45173</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45173</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>46185</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46188</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44586</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45385</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45240</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45250</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44740</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45266</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45317</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44802</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45293</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45435</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>46273</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44802</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45562</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44802</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45371</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45617</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44873</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45090</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45216</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44934</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45293</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45783</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45419</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45428</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44663</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45390</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45565</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45485</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45571</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44859</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>15</v>
@@ -1067,13 +1067,13 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="U5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1102,6 +1102,7 @@
 Grovticka
 Guldkremla
 Hasselticka
+Igelkottsröksvamp
 Toppvaxing
 Vanlig groda</t>
         </is>
@@ -1155,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1420,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1549,7 +1550,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1667,7 +1668,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1789,7 +1790,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1907,7 @@
         <v>46178</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2028,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2149,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2260,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2370,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2480,7 @@
         <v>45874</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2599,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2718,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2828,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2943,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3051,7 +3052,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3161,7 @@
         <v>45933</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3278,7 +3279,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3390,7 +3391,7 @@
         <v>45940</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3503,7 +3504,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3620,7 @@
         <v>44656</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3728,7 @@
         <v>45267</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3836,7 @@
         <v>44744</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3942,7 +3943,7 @@
         <v>45933</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4058,7 +4059,7 @@
         <v>44520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4166,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4272,7 +4273,7 @@
         <v>45145</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4383,7 +4384,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4495,7 +4496,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4605,7 +4606,7 @@
         <v>45471</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4717,7 @@
         <v>45967</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4826,7 +4827,7 @@
         <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4932,7 +4933,7 @@
         <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5038,7 +5039,7 @@
         <v>45184</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5149,7 +5150,7 @@
         <v>44475</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5255,7 +5256,7 @@
         <v>45720</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5365,7 +5366,7 @@
         <v>45751</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5471,7 +5472,7 @@
         <v>44673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5582,7 +5583,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5694,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5800,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5911,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6019,7 +6020,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6130,7 @@
         <v>44903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6239,7 +6240,7 @@
         <v>45902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6349,7 @@
         <v>45793</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6458,7 @@
         <v>45119</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6568,7 @@
         <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6681,7 +6682,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6791,7 +6792,7 @@
         <v>45385</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6901,7 +6902,7 @@
         <v>45218</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7007,7 @@
         <v>45009</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7117,7 @@
         <v>45470</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7226,7 +7227,7 @@
         <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7336,7 +7337,7 @@
         <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7441,7 +7442,7 @@
         <v>46239</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7546,7 +7547,7 @@
         <v>45432</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7656,7 +7657,7 @@
         <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7761,7 +7762,7 @@
         <v>44868</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7871,7 +7872,7 @@
         <v>44790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7980,7 +7981,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8089,7 +8090,7 @@
         <v>44874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8162,7 +8163,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8236,7 @@
         <v>44586</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8309,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,7 +8382,7 @@
         <v>44671</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8454,7 +8455,7 @@
         <v>44774</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8527,7 +8528,7 @@
         <v>44586</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8600,7 +8601,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8673,7 +8674,7 @@
         <v>44744</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8746,7 +8747,7 @@
         <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8819,7 +8820,7 @@
         <v>45428</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8892,7 +8893,7 @@
         <v>46006</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8965,7 +8966,7 @@
         <v>46006</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9038,7 +9039,7 @@
         <v>46027</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9111,7 +9112,7 @@
         <v>46027</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9184,7 +9185,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9257,7 +9258,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9330,7 +9331,7 @@
         <v>46034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9403,7 +9404,7 @@
         <v>46034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9476,7 +9477,7 @@
         <v>45371</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9549,7 +9550,7 @@
         <v>46037</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9622,7 +9623,7 @@
         <v>45243</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9695,7 +9696,7 @@
         <v>45173</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9768,7 +9769,7 @@
         <v>45173</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9841,7 +9842,7 @@
         <v>45317</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9914,7 +9915,7 @@
         <v>45604</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9987,7 +9988,7 @@
         <v>44744</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10060,7 +10061,7 @@
         <v>46057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10133,7 +10134,7 @@
         <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10211,7 +10212,7 @@
         <v>46041</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10284,7 +10285,7 @@
         <v>46070</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10357,7 +10358,7 @@
         <v>45104</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10430,7 +10431,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10508,7 +10509,7 @@
         <v>46077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10581,7 +10582,7 @@
         <v>46077</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10654,7 +10655,7 @@
         <v>46077</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10727,7 +10728,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10800,7 +10801,7 @@
         <v>46077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10873,7 +10874,7 @@
         <v>46077</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10946,7 +10947,7 @@
         <v>46086</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11019,7 +11020,7 @@
         <v>46086</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11092,7 +11093,7 @@
         <v>44873</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11170,7 +11171,7 @@
         <v>45177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11243,7 +11244,7 @@
         <v>44810</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11316,7 +11317,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11389,7 +11390,7 @@
         <v>46098</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11462,7 +11463,7 @@
         <v>44956</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11535,7 +11536,7 @@
         <v>46108</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11608,7 +11609,7 @@
         <v>45481</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11681,7 +11682,7 @@
         <v>45293</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11754,7 +11755,7 @@
         <v>46132</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11827,7 +11828,7 @@
         <v>46132</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11900,7 +11901,7 @@
         <v>45385</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11973,7 +11974,7 @@
         <v>45470</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12051,7 +12052,7 @@
         <v>45103</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12124,7 +12125,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12197,7 +12198,7 @@
         <v>45316</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12270,7 +12271,7 @@
         <v>45043</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12343,7 +12344,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12416,7 +12417,7 @@
         <v>45243</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12489,7 +12490,7 @@
         <v>45505</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12567,7 +12568,7 @@
         <v>45799</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12640,7 +12641,7 @@
         <v>45799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12713,7 +12714,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12786,7 +12787,7 @@
         <v>44934</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12859,7 +12860,7 @@
         <v>45145</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12932,7 +12933,7 @@
         <v>46140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13005,7 +13006,7 @@
         <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13078,7 +13079,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13151,7 +13152,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13224,7 +13225,7 @@
         <v>45250</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13297,7 +13298,7 @@
         <v>46148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13370,7 +13371,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13443,7 +13444,7 @@
         <v>45298</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13516,7 +13517,7 @@
         <v>45197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13589,7 +13590,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13662,7 +13663,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13735,7 +13736,7 @@
         <v>45226</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13813,7 +13814,7 @@
         <v>46030</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13886,7 +13887,7 @@
         <v>46176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13964,7 +13965,7 @@
         <v>45644</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14037,7 +14038,7 @@
         <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14110,7 +14111,7 @@
         <v>46188</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14183,7 +14184,7 @@
         <v>45266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14256,7 +14257,7 @@
         <v>45090</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14329,7 +14330,7 @@
         <v>46195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14402,7 +14403,7 @@
         <v>45293</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14475,7 +14476,7 @@
         <v>45293</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14548,7 +14549,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14621,7 +14622,7 @@
         <v>45726</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14694,7 +14695,7 @@
         <v>45617</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14767,7 +14768,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14840,7 +14841,7 @@
         <v>45562</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14918,7 +14919,7 @@
         <v>44859</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14996,7 +14997,7 @@
         <v>45524</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15069,7 +15070,7 @@
         <v>44740</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15142,7 +15143,7 @@
         <v>46273</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15215,7 +15216,7 @@
         <v>44485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15288,7 +15289,7 @@
         <v>46239</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15361,7 +15362,7 @@
         <v>44602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15434,7 +15435,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15507,7 +15508,7 @@
         <v>44802</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15580,7 +15581,7 @@
         <v>45317</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15653,7 +15654,7 @@
         <v>44724</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15726,7 +15727,7 @@
         <v>44544</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15799,7 +15800,7 @@
         <v>45435</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15877,7 +15878,7 @@
         <v>44802</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15950,7 +15951,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16023,7 +16024,7 @@
         <v>45216</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16096,7 +16097,7 @@
         <v>45524</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16169,7 +16170,7 @@
         <v>44956</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16242,7 +16243,7 @@
         <v>45671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16315,7 +16316,7 @@
         <v>44844</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16388,7 +16389,7 @@
         <v>44943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16461,7 +16462,7 @@
         <v>44802</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16534,7 +16535,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16607,7 +16608,7 @@
         <v>45453</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16680,7 +16681,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16753,7 +16754,7 @@
         <v>45783</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16826,7 +16827,7 @@
         <v>44855</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16899,7 +16900,7 @@
         <v>44859</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16977,7 +16978,7 @@
         <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17050,7 +17051,7 @@
         <v>44663</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17128,7 +17129,7 @@
         <v>45565</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17201,7 +17202,7 @@
         <v>45485</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17274,7 +17275,7 @@
         <v>45571</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17347,7 +17348,7 @@
         <v>44859</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>46178</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45874</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45492</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45933</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45940</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44656</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45267</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44744</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45933</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>44810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45145</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45471</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45967</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45145</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45184</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>44475</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45720</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45751</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44859</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45793</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45119</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>45385</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45218</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45009</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45470</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>46239</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45432</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44868</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45901</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>44874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44586</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44671</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44774</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44586</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44744</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45428</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>46006</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>46006</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>46027</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>46027</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>46034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45371</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>46037</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45243</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45173</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45173</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45317</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45604</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44744</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>46057</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>46041</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>46070</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45104</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>46077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>46077</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46077</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>46077</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>46077</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>46077</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46086</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>46086</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44873</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45177</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44810</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>46098</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44956</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>46108</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45481</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45293</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>46132</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46132</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45385</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45470</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45103</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45316</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45043</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45243</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45505</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45799</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45799</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44934</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45145</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>46140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45250</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>46148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45298</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45226</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>46030</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>46176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45644</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>46188</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45090</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45293</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45293</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45726</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45617</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45562</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44859</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45524</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44740</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>46273</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>46239</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44802</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>45317</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44724</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44544</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45435</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44802</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45216</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45524</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44956</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>44844</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44802</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45453</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45716</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45783</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44855</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44859</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44663</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45565</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45485</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45571</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44859</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44589</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>46178</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45148</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46162</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45293</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44744</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45933</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45940</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44656</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44744</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45933</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44520</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45145</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45967</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44868</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45751</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>45119</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45902</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45385</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45009</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45470</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45432</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>46239</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44790</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45793</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>46304</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44744</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45371</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45243</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45173</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45173</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44744</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44873</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44956</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45293</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45470</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45103</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>46140</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46140</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>46140</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44977</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45316</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45043</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45243</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45505</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>46148</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45932</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45145</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45250</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>46077</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>44564</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45298</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45197</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44802</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45226</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46006</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45644</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46027</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46027</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46027</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46027</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46176</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46057</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45293</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45293</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46188</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46041</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>46070</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44865</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46076</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46077</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46077</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>46077</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46077</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45617</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>46086</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>46086</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44844</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>46098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45562</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46195</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45524</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46132</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46132</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44602</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44802</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44724</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45435</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44802</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45240</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>46239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45216</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45524</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44956</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44844</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44802</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45541</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45453</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45716</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46300</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45783</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44855</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45419</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45428</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46309</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44859</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45390</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44663</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44859</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44840</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44589</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44589</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>46178</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45148</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46162</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45293</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44744</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45933</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45940</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44656</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44744</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45933</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44520</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45145</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45967</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45720</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44868</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45751</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>45119</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45902</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45385</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45009</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45470</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>45432</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>46239</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44790</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45793</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>46304</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44744</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45371</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45243</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45173</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45173</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44744</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44873</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44956</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45293</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45470</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45103</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>46140</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46140</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>46140</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44977</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45316</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45043</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45243</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45505</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>46148</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45932</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45145</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45250</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>46077</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>44564</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45298</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45197</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44802</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45226</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46006</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45644</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46027</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46027</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46027</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46027</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46176</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46057</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45293</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45293</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46188</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>46041</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>46070</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44865</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46076</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46077</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46077</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>46077</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46077</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45617</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>46086</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>46086</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44844</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>46098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45562</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46195</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45524</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44740</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46132</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46132</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44602</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44802</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44724</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45435</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44802</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45240</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>46239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45216</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45524</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44956</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44844</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44802</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45541</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45453</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45716</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46300</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45783</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44855</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45419</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45428</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46309</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44859</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45390</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44663</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44859</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44840</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46178</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46162</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45293</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45933</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45267</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44656</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45933</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>44810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44520</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45967</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44868</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45471</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45145</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45902</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45470</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44790</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45793</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46304</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45385</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45119</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45432</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45243</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45218</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45371</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>46077</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45481</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44873</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45145</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45103</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45243</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>46176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45524</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46185</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>46195</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44956</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45293</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45317</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45470</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>46006</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45783</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45419</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44855</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45428</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>46027</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46027</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46027</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>46239</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>46034</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45604</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45154</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45293</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>46041</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46077</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46077</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46077</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>46077</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>46086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46300</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>46098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46108</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>46132</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>46132</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45453</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>46309</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>46140</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44544</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45799</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45505</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46273</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46140</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45541</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46140</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>46140</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45799</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44943</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44744</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>46148</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44956</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>44744</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45316</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44844</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45243</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44844</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45524</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44602</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45298</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45726</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44724</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45173</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45385</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45250</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44740</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45317</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44802</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45293</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45435</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44802</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>44859</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44802</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44663</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45390</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44859</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>

--- a/Översikt SÖDERTÄLJE.xlsx
+++ b/Översikt SÖDERTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>45916</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45916</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>44901</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45817</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44840</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46178</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46162</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45148</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45980</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45293</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45874</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45492</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45933</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>44744</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45267</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44656</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45933</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>44810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44520</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>44744</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45817</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45967</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44868</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45471</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45145</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45751</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>44824</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45902</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45470</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44790</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45793</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46304</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45385</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45119</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45432</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45243</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45218</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45901</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44509</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45371</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45266</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44802</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>46077</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45481</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44873</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45145</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45103</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45243</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>46176</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45524</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46185</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>46195</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45216</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44956</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45293</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45317</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45470</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>46006</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45783</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45419</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44855</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45428</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>46027</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46027</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46027</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>46239</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>46034</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45604</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45154</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45293</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>46041</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46077</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>46077</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46077</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>46077</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>46086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46300</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>46098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46108</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>46132</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>46132</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45453</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>46309</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>46140</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44544</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45799</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45505</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46273</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46140</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45541</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46140</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>46140</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45799</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44943</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44744</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>46148</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>44956</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>44744</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45316</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44844</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44571</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45243</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44844</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45524</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44602</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45298</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45726</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44724</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45173</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45385</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45250</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44740</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45317</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44802</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45293</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45435</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44802</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>44859</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44802</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44663</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45390</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45485</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44859</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
